--- a/03_analysis_input/stratification_info.xlsx
+++ b/03_analysis_input/stratification_info.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F521"/>
+  <dimension ref="A1:F525"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>30039</t>
+          <t>30040</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="D90">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>30040</t>
+          <t>30041</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2868,11 +2868,11 @@
         </is>
       </c>
       <c r="D91">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>30041</t>
+          <t>30042</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>30042</t>
+          <t>30044</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2918,7 +2918,7 @@
         </is>
       </c>
       <c r="D93">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>30044</t>
+          <t>30045</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2943,11 +2943,11 @@
         </is>
       </c>
       <c r="D94">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>30045</t>
+          <t>30046</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="D95">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>30047</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2993,11 +2993,11 @@
         </is>
       </c>
       <c r="D96">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>30048</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3018,11 +3018,11 @@
         </is>
       </c>
       <c r="D97">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>30047</t>
+          <t>30049</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>30048</t>
+          <t>30050</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="D99">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>30049</t>
+          <t>30051</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3093,11 +3093,11 @@
         </is>
       </c>
       <c r="D100">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>30050</t>
+          <t>30052</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="D101">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>30051</t>
+          <t>30053</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="D102">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>30052</t>
+          <t>30054</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="D103">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>30053</t>
+          <t>30056</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="D104">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>30054</t>
+          <t>30057</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="D105">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>30056</t>
+          <t>30058</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="D106">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>30057</t>
+          <t>30059</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3268,11 +3268,11 @@
         </is>
       </c>
       <c r="D107">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>30058</t>
+          <t>30061</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>30059</t>
+          <t>30062</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3318,11 +3318,11 @@
         </is>
       </c>
       <c r="D109">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>30061</t>
+          <t>30063</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3343,11 +3343,11 @@
         </is>
       </c>
       <c r="D110">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>30062</t>
+          <t>30064</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3368,11 +3368,11 @@
         </is>
       </c>
       <c r="D111">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>30063</t>
+          <t>30065</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3393,11 +3393,11 @@
         </is>
       </c>
       <c r="D112">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>30064</t>
+          <t>30066</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3418,11 +3418,11 @@
         </is>
       </c>
       <c r="D113">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>30065</t>
+          <t>30067</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3443,11 +3443,11 @@
         </is>
       </c>
       <c r="D114">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>30066</t>
+          <t>30068</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3468,7 +3468,7 @@
         </is>
       </c>
       <c r="D115">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>30067</t>
+          <t>30069</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>30068</t>
+          <t>30070</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>30069</t>
+          <t>30071</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="D118">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>30070</t>
+          <t>30072</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3568,11 +3568,11 @@
         </is>
       </c>
       <c r="D119">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>30071</t>
+          <t>30073</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="D120">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>30072</t>
+          <t>30074</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="D121">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>30073</t>
+          <t>30075</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>30073</t>
+          <t>30076</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3668,7 +3668,7 @@
         </is>
       </c>
       <c r="D123">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>30074</t>
+          <t>30077</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3693,11 +3693,11 @@
         </is>
       </c>
       <c r="D124">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>30075</t>
+          <t>30078</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="D125">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>30076</t>
+          <t>30079</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="D126">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>30077</t>
+          <t>30081</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="D127">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>30082</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="D128">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>30079</t>
+          <t>30083</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="D129">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>30081</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="D130">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>30082</t>
+          <t>30085</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3868,11 +3868,11 @@
         </is>
       </c>
       <c r="D131">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>30083</t>
+          <t>30086</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="D132">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>30084</t>
+          <t>30087</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3918,7 +3918,7 @@
         </is>
       </c>
       <c r="D133">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>30085</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3943,11 +3943,11 @@
         </is>
       </c>
       <c r="D134">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>30086</t>
+          <t>30089</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="D135">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>30087</t>
+          <t>30092</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="D136">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>30088</t>
+          <t>30093</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4018,11 +4018,11 @@
         </is>
       </c>
       <c r="D137">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>30089</t>
+          <t>30094</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4043,11 +4043,11 @@
         </is>
       </c>
       <c r="D138">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>30092</t>
+          <t>30095</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4068,11 +4068,11 @@
         </is>
       </c>
       <c r="D139">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>30093</t>
+          <t>30096</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4093,11 +4093,11 @@
         </is>
       </c>
       <c r="D140">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>30094</t>
+          <t>30098</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4118,11 +4118,11 @@
         </is>
       </c>
       <c r="D141">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>30095</t>
+          <t>30099</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4143,11 +4143,11 @@
         </is>
       </c>
       <c r="D142">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>30096</t>
+          <t>30100</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="D143">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>30098</t>
+          <t>30100</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4193,11 +4193,11 @@
         </is>
       </c>
       <c r="D144">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>30099</t>
+          <t>30101</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="D145">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4234,16 +4234,13 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>30100</t>
+          <t>30102</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
           <t>3</t>
         </is>
-      </c>
-      <c r="D146">
-        <v>27</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -4259,7 +4256,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>30100</t>
+          <t>30103</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4268,11 +4265,11 @@
         </is>
       </c>
       <c r="D147">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4281,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>30101</t>
+          <t>30104</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4293,11 +4290,11 @@
         </is>
       </c>
       <c r="D148">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -4309,13 +4306,16 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>30102</t>
+          <t>30105</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
           <t>3</t>
         </is>
+      </c>
+      <c r="D149">
+        <v>22</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>30103</t>
+          <t>30106</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="D150">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>30104</t>
+          <t>30107</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>30105</t>
+          <t>30108</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="D152">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>30106</t>
+          <t>30109</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4415,11 +4415,11 @@
         </is>
       </c>
       <c r="D153">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>30107</t>
+          <t>30110</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>30108</t>
+          <t>30111</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="D155">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>30109</t>
+          <t>30112</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4490,11 +4490,11 @@
         </is>
       </c>
       <c r="D156">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>30110</t>
+          <t>30113</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="D157">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>30111</t>
+          <t>30114</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="D158">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>30112</t>
+          <t>30115</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4565,11 +4565,11 @@
         </is>
       </c>
       <c r="D159">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>30113</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>30114</t>
+          <t>30118</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="D161">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>30115</t>
+          <t>30119</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4640,11 +4640,11 @@
         </is>
       </c>
       <c r="D162">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>30117</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4665,11 +4665,11 @@
         </is>
       </c>
       <c r="D163">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>30118</t>
+          <t>30121</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4690,11 +4690,11 @@
         </is>
       </c>
       <c r="D164">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>30119</t>
+          <t>30122</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="D165">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>30123</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="D166">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>30121</t>
+          <t>30124</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4765,11 +4765,11 @@
         </is>
       </c>
       <c r="D167">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>30122</t>
+          <t>30125</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="D168">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>30123</t>
+          <t>30126</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="D169">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>30124</t>
+          <t>30127</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4840,12 +4840,7 @@
         </is>
       </c>
       <c r="D170">
-        <v>27</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
+        <v>20</v>
       </c>
     </row>
     <row r="171">
@@ -4856,7 +4851,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>30125</t>
+          <t>30128</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4865,7 +4860,7 @@
         </is>
       </c>
       <c r="D171">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -4881,7 +4876,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>30126</t>
+          <t>32039</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4890,11 +4885,11 @@
         </is>
       </c>
       <c r="D172">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4901,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>30127</t>
+          <t>32046</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4915,7 +4910,12 @@
         </is>
       </c>
       <c r="D173">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
       </c>
     </row>
     <row r="174">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>30128</t>
+          <t>32070</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="D174">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -4976,16 +4976,16 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>32072</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D176">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -5001,16 +5001,21 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>40001</t>
+          <t>32073</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D177">
-        <v>37</v>
+        <v>26</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
       </c>
     </row>
     <row r="178">
@@ -5021,20 +5026,20 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>40002</t>
+          <t>32078</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D178">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5051,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>40003</t>
+          <t>40001</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5055,12 +5060,7 @@
         </is>
       </c>
       <c r="D179">
-        <v>19</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
+        <v>37</v>
       </c>
     </row>
     <row r="180">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>40004</t>
+          <t>40002</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5080,11 +5080,11 @@
         </is>
       </c>
       <c r="D180">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>40005</t>
+          <t>40003</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5105,11 +5105,11 @@
         </is>
       </c>
       <c r="D181">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>40006</t>
+          <t>40004</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5130,11 +5130,11 @@
         </is>
       </c>
       <c r="D182">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>40007</t>
+          <t>40005</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="D183">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>40008</t>
+          <t>40006</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5180,11 +5180,11 @@
         </is>
       </c>
       <c r="D184">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>40009</t>
+          <t>40007</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="D185">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>40010</t>
+          <t>40008</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5230,7 +5230,7 @@
         </is>
       </c>
       <c r="D186">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>40011</t>
+          <t>40009</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="D187">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>40013</t>
+          <t>40010</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>40014</t>
+          <t>40011</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5305,11 +5305,11 @@
         </is>
       </c>
       <c r="D189">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>40015</t>
+          <t>40013</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="D190">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>40016</t>
+          <t>40014</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5355,11 +5355,11 @@
         </is>
       </c>
       <c r="D191">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>40017</t>
+          <t>40015</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5380,11 +5380,11 @@
         </is>
       </c>
       <c r="D192">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>40018</t>
+          <t>40016</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="D193">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>40019</t>
+          <t>40017</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5430,11 +5430,11 @@
         </is>
       </c>
       <c r="D194">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>40020</t>
+          <t>40018</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5455,11 +5455,11 @@
         </is>
       </c>
       <c r="D195">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>40021</t>
+          <t>40019</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="D196">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>40022</t>
+          <t>40020</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5505,11 +5505,11 @@
         </is>
       </c>
       <c r="D197">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>40023</t>
+          <t>40021</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5530,11 +5530,11 @@
         </is>
       </c>
       <c r="D198">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>40024</t>
+          <t>40022</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5555,7 +5555,7 @@
         </is>
       </c>
       <c r="D199">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>40026</t>
+          <t>40023</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5580,7 +5580,7 @@
         </is>
       </c>
       <c r="D200">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>40027</t>
+          <t>40024</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5605,11 +5605,11 @@
         </is>
       </c>
       <c r="D201">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>40028</t>
+          <t>40026</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5630,11 +5630,11 @@
         </is>
       </c>
       <c r="D202">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>40029</t>
+          <t>40027</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5655,11 +5655,11 @@
         </is>
       </c>
       <c r="D203">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>40030</t>
+          <t>40028</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5680,11 +5680,11 @@
         </is>
       </c>
       <c r="D204">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>40031</t>
+          <t>40029</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="D205">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>40032</t>
+          <t>40030</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5730,11 +5730,11 @@
         </is>
       </c>
       <c r="D206">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>40034</t>
+          <t>40031</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="D207">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>40035</t>
+          <t>40032</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="D208">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>40036</t>
+          <t>40033</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5805,11 +5805,11 @@
         </is>
       </c>
       <c r="D209">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>40037</t>
+          <t>40034</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5830,11 +5830,11 @@
         </is>
       </c>
       <c r="D210">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>40038</t>
+          <t>40035</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5855,7 +5855,7 @@
         </is>
       </c>
       <c r="D211">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>40039</t>
+          <t>40036</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5880,11 +5880,11 @@
         </is>
       </c>
       <c r="D212">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>40040</t>
+          <t>40037</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>40041</t>
+          <t>40038</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="D214">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>40042</t>
+          <t>40039</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5955,11 +5955,11 @@
         </is>
       </c>
       <c r="D215">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>40043</t>
+          <t>40040</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5980,7 +5980,7 @@
         </is>
       </c>
       <c r="D216">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>40044</t>
+          <t>40041</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="D217">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>40045</t>
+          <t>40042</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6030,11 +6030,11 @@
         </is>
       </c>
       <c r="D218">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>40046</t>
+          <t>40043</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6055,11 +6055,11 @@
         </is>
       </c>
       <c r="D219">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>40047</t>
+          <t>40044</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="D220">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>40048</t>
+          <t>40045</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6105,7 +6105,12 @@
         </is>
       </c>
       <c r="D221">
-        <v>42</v>
+        <v>25</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
       </c>
     </row>
     <row r="222">
@@ -6116,7 +6121,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>40049</t>
+          <t>40046</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6125,7 +6130,7 @@
         </is>
       </c>
       <c r="D222">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -6141,7 +6146,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>40050</t>
+          <t>40047</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6150,7 +6155,7 @@
         </is>
       </c>
       <c r="D223">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -6166,7 +6171,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>40051</t>
+          <t>40048</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6175,12 +6180,7 @@
         </is>
       </c>
       <c r="D224">
-        <v>22</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
+        <v>42</v>
       </c>
     </row>
     <row r="225">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>40052</t>
+          <t>40049</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6200,11 +6200,11 @@
         </is>
       </c>
       <c r="D225">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>40053</t>
+          <t>40050</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="D226">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>40054</t>
+          <t>40051</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6250,11 +6250,11 @@
         </is>
       </c>
       <c r="D227">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>40055</t>
+          <t>40052</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -6275,7 +6275,7 @@
         </is>
       </c>
       <c r="D228">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -6291,20 +6291,20 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>50001</t>
+          <t>40053</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D229">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -6316,20 +6316,20 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>50002</t>
+          <t>40054</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D230">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -6341,20 +6341,20 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>50003</t>
+          <t>40055</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D231">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>50004</t>
+          <t>50001</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6375,11 +6375,11 @@
         </is>
       </c>
       <c r="D232">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>50005</t>
+          <t>50002</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c r="D233">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>50006</t>
+          <t>50003</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="D234">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>50007</t>
+          <t>50004</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -6450,7 +6450,7 @@
         </is>
       </c>
       <c r="D235">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>50008</t>
+          <t>50005</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="D236">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>50009</t>
+          <t>50006</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="D237">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>50010</t>
+          <t>50007</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -6525,11 +6525,11 @@
         </is>
       </c>
       <c r="D238">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>50011</t>
+          <t>50008</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -6550,11 +6550,11 @@
         </is>
       </c>
       <c r="D239">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>50012</t>
+          <t>50009</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -6575,11 +6575,11 @@
         </is>
       </c>
       <c r="D240">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>50013</t>
+          <t>50010</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -6600,11 +6600,11 @@
         </is>
       </c>
       <c r="D241">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>50014</t>
+          <t>50011</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -6625,11 +6625,11 @@
         </is>
       </c>
       <c r="D242">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>50015</t>
+          <t>50012</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -6650,11 +6650,11 @@
         </is>
       </c>
       <c r="D243">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>50016</t>
+          <t>50013</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>50017</t>
+          <t>50014</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -6700,7 +6700,7 @@
         </is>
       </c>
       <c r="D245">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>50018</t>
+          <t>50015</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -6725,11 +6725,11 @@
         </is>
       </c>
       <c r="D246">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>50019</t>
+          <t>50016</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="D247">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>50017</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -6775,11 +6775,11 @@
         </is>
       </c>
       <c r="D248">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>50021</t>
+          <t>50018</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -6800,7 +6800,7 @@
         </is>
       </c>
       <c r="D249">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>50022</t>
+          <t>50019</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -6825,11 +6825,11 @@
         </is>
       </c>
       <c r="D250">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>50023</t>
+          <t>50020</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -6850,11 +6850,11 @@
         </is>
       </c>
       <c r="D251">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>50024</t>
+          <t>50021</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -6875,11 +6875,11 @@
         </is>
       </c>
       <c r="D252">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>50025</t>
+          <t>50022</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -6900,11 +6900,11 @@
         </is>
       </c>
       <c r="D253">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>50026</t>
+          <t>50023</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6925,11 +6925,11 @@
         </is>
       </c>
       <c r="D254">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>50027</t>
+          <t>50024</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="D255">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>50028</t>
+          <t>50025</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="D256">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -6991,12 +6991,20 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>50029</t>
+          <t>50026</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
           <t>5</t>
+        </is>
+      </c>
+      <c r="D257">
+        <v>41</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7016,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>50030</t>
+          <t>50027</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -7017,11 +7025,11 @@
         </is>
       </c>
       <c r="D258">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -7033,7 +7041,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>50031</t>
+          <t>50028</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -7042,11 +7050,11 @@
         </is>
       </c>
       <c r="D259">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -7058,20 +7066,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>50032</t>
+          <t>50029</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D260">
-        <v>25</v>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>male</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>50033</t>
+          <t>50030</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -7092,7 +7092,7 @@
         </is>
       </c>
       <c r="D261">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>50034</t>
+          <t>50031</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -7117,11 +7117,11 @@
         </is>
       </c>
       <c r="D262">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>50035</t>
+          <t>50032</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -7142,11 +7142,11 @@
         </is>
       </c>
       <c r="D263">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>50036</t>
+          <t>50033</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -7167,11 +7167,11 @@
         </is>
       </c>
       <c r="D264">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>50037</t>
+          <t>50034</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -7192,11 +7192,11 @@
         </is>
       </c>
       <c r="D265">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>50038</t>
+          <t>50035</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -7217,11 +7217,11 @@
         </is>
       </c>
       <c r="D266">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>50039</t>
+          <t>50036</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>50040</t>
+          <t>50037</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -7267,11 +7267,11 @@
         </is>
       </c>
       <c r="D268">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -7283,7 +7283,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>50041</t>
+          <t>50038</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="D269">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>50042</t>
+          <t>50039</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -7317,11 +7317,11 @@
         </is>
       </c>
       <c r="D270">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>50043</t>
+          <t>50040</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="D271">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>50044</t>
+          <t>50041</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -7367,11 +7367,11 @@
         </is>
       </c>
       <c r="D272">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>50045</t>
+          <t>50042</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -7392,11 +7392,11 @@
         </is>
       </c>
       <c r="D273">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>50046</t>
+          <t>50043</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -7417,7 +7417,7 @@
         </is>
       </c>
       <c r="D274">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>50047</t>
+          <t>50044</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="D275">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>50048</t>
+          <t>50045</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -7467,11 +7467,11 @@
         </is>
       </c>
       <c r="D276">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>50049</t>
+          <t>50046</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -7492,7 +7492,7 @@
         </is>
       </c>
       <c r="D277">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>50050</t>
+          <t>50047</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -7517,11 +7517,11 @@
         </is>
       </c>
       <c r="D278">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -7533,7 +7533,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>50051</t>
+          <t>50048</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -7542,11 +7542,11 @@
         </is>
       </c>
       <c r="D279">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>50052</t>
+          <t>50049</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>50053</t>
+          <t>50050</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="D281">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>50054</t>
+          <t>50051</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="D282">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>50201</t>
+          <t>50052</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="D283">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -7658,12 +7658,20 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>50201</t>
+          <t>50053</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
           <t>5</t>
+        </is>
+      </c>
+      <c r="D284">
+        <v>36</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7683,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>50202</t>
+          <t>50054</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -7684,7 +7692,7 @@
         </is>
       </c>
       <c r="D285">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -7700,7 +7708,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>50203</t>
+          <t>50055</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -7709,7 +7717,7 @@
         </is>
       </c>
       <c r="D286">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -7725,7 +7733,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>50204</t>
+          <t>50201</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -7734,11 +7742,11 @@
         </is>
       </c>
       <c r="D287">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -7750,20 +7758,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>50205</t>
+          <t>50201</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D288">
-        <v>33</v>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>male</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>50206</t>
+          <t>50202</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="D289">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>50207</t>
+          <t>50203</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="D290">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>50208</t>
+          <t>50204</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="D291">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>50209</t>
+          <t>50205</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -7859,7 +7859,7 @@
         </is>
       </c>
       <c r="D292">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -7875,20 +7875,20 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>70003</t>
+          <t>50206</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D293">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -7900,20 +7900,20 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>70004</t>
+          <t>50207</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D294">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -7925,16 +7925,16 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>70005</t>
+          <t>50208</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D295">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -7950,20 +7950,20 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>70006</t>
+          <t>50209</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D296">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>70007</t>
+          <t>70003</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>70009</t>
+          <t>70004</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -8009,7 +8009,7 @@
         </is>
       </c>
       <c r="D298">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>70010</t>
+          <t>70005</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -8034,7 +8034,7 @@
         </is>
       </c>
       <c r="D299">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>70011</t>
+          <t>70006</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -8075,7 +8075,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>70012</t>
+          <t>70007</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="D301">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>70013</t>
+          <t>70009</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -8109,7 +8109,7 @@
         </is>
       </c>
       <c r="D302">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>70014</t>
+          <t>70010</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -8134,7 +8134,7 @@
         </is>
       </c>
       <c r="D303">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>70018</t>
+          <t>70011</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -8159,11 +8159,11 @@
         </is>
       </c>
       <c r="D304">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>70020</t>
+          <t>70012</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -8184,11 +8184,11 @@
         </is>
       </c>
       <c r="D305">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>70021</t>
+          <t>70013</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -8209,7 +8209,7 @@
         </is>
       </c>
       <c r="D306">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>70024</t>
+          <t>70014</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -8234,11 +8234,11 @@
         </is>
       </c>
       <c r="D307">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>70025</t>
+          <t>70018</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="D308">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>70028</t>
+          <t>70020</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -8284,7 +8284,7 @@
         </is>
       </c>
       <c r="D309">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>70029</t>
+          <t>70021</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="D310">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>70030</t>
+          <t>70024</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -8334,11 +8334,11 @@
         </is>
       </c>
       <c r="D311">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>70035</t>
+          <t>70025</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="D312">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>70040</t>
+          <t>70028</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -8384,11 +8384,11 @@
         </is>
       </c>
       <c r="D313">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>70041</t>
+          <t>70029</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -8409,11 +8409,11 @@
         </is>
       </c>
       <c r="D314">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>70049</t>
+          <t>70030</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -8434,7 +8434,7 @@
         </is>
       </c>
       <c r="D315">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>70054</t>
+          <t>70035</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -8459,11 +8459,11 @@
         </is>
       </c>
       <c r="D316">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>70055</t>
+          <t>70040</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="D317">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>70059</t>
+          <t>70041</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>70060</t>
+          <t>70049</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -8534,7 +8534,7 @@
         </is>
       </c>
       <c r="D319">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>70061</t>
+          <t>70054</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -8559,11 +8559,11 @@
         </is>
       </c>
       <c r="D320">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>70067</t>
+          <t>70055</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="D321">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>70079</t>
+          <t>70059</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -8609,11 +8609,11 @@
         </is>
       </c>
       <c r="D322">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -8625,7 +8625,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>70080</t>
+          <t>70060</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -8634,11 +8634,11 @@
         </is>
       </c>
       <c r="D323">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>70082</t>
+          <t>70061</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -8659,7 +8659,7 @@
         </is>
       </c>
       <c r="D324">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>70095</t>
+          <t>70067</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -8684,11 +8684,11 @@
         </is>
       </c>
       <c r="D325">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>70096</t>
+          <t>70079</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="D326">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>70097</t>
+          <t>70080</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>70101</t>
+          <t>70082</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -8759,7 +8759,7 @@
         </is>
       </c>
       <c r="D328">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>70103</t>
+          <t>70095</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>70111</t>
+          <t>70096</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -8809,7 +8809,12 @@
         </is>
       </c>
       <c r="D330">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
       </c>
     </row>
     <row r="331">
@@ -8820,7 +8825,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>70129</t>
+          <t>70097</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -8829,7 +8834,7 @@
         </is>
       </c>
       <c r="D331">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -8845,7 +8850,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>70130</t>
+          <t>70101</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -8854,7 +8859,7 @@
         </is>
       </c>
       <c r="D332">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -8870,7 +8875,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>70134</t>
+          <t>70103</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -8879,7 +8884,7 @@
         </is>
       </c>
       <c r="D333">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -8895,7 +8900,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>70137</t>
+          <t>70111</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -8904,12 +8909,7 @@
         </is>
       </c>
       <c r="D334">
-        <v>29</v>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
+        <v>28</v>
       </c>
     </row>
     <row r="335">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>70139</t>
+          <t>70129</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -8929,11 +8929,11 @@
         </is>
       </c>
       <c r="D335">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -8945,7 +8945,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>70149</t>
+          <t>70130</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -8954,11 +8954,11 @@
         </is>
       </c>
       <c r="D336">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -8970,13 +8970,16 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>70153</t>
+          <t>70134</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
           <t>7</t>
         </is>
+      </c>
+      <c r="D337">
+        <v>25</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -8992,7 +8995,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>70168</t>
+          <t>70137</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -9001,7 +9004,7 @@
         </is>
       </c>
       <c r="D338">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -9017,25 +9020,20 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>80002</t>
+          <t>70139</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D339">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>HC</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -9047,25 +9045,20 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>80003</t>
+          <t>70149</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D340">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>male</t>
-        </is>
-      </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>HC</t>
         </is>
       </c>
     </row>
@@ -9077,25 +9070,17 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>80004</t>
+          <t>70153</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D341">
-        <v>23</v>
+          <t>7</t>
+        </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>HC</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -9107,25 +9092,20 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>70168</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D342">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>female</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>HC</t>
         </is>
       </c>
     </row>
@@ -9137,7 +9117,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>80006</t>
+          <t>80002</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -9146,11 +9126,11 @@
         </is>
       </c>
       <c r="D343">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -9167,7 +9147,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>80007</t>
+          <t>80003</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -9176,11 +9156,11 @@
         </is>
       </c>
       <c r="D344">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -9197,7 +9177,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>80008</t>
+          <t>80004</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -9206,7 +9186,7 @@
         </is>
       </c>
       <c r="D345">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -9227,7 +9207,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>80010</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -9236,7 +9216,7 @@
         </is>
       </c>
       <c r="D346">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -9257,7 +9237,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>80011</t>
+          <t>80006</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -9266,11 +9246,11 @@
         </is>
       </c>
       <c r="D347">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -9287,7 +9267,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>80011</t>
+          <t>80007</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -9296,7 +9276,7 @@
         </is>
       </c>
       <c r="D348">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -9317,7 +9297,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>80012</t>
+          <t>80008</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -9326,11 +9306,11 @@
         </is>
       </c>
       <c r="D349">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -9347,7 +9327,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>80013</t>
+          <t>80010</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -9356,7 +9336,7 @@
         </is>
       </c>
       <c r="D350">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -9377,7 +9357,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>80014</t>
+          <t>80012</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -9386,11 +9366,11 @@
         </is>
       </c>
       <c r="D351">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -9407,7 +9387,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>80015</t>
+          <t>80013</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -9416,11 +9396,11 @@
         </is>
       </c>
       <c r="D352">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -9437,7 +9417,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>80016</t>
+          <t>80014</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -9446,7 +9426,7 @@
         </is>
       </c>
       <c r="D353">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
@@ -9467,7 +9447,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>80017</t>
+          <t>80015</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -9476,11 +9456,11 @@
         </is>
       </c>
       <c r="D354">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -9497,7 +9477,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>80019</t>
+          <t>80016</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -9506,7 +9486,7 @@
         </is>
       </c>
       <c r="D355">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -9527,7 +9507,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>80020</t>
+          <t>80017</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -9536,7 +9516,7 @@
         </is>
       </c>
       <c r="D356">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
@@ -9557,7 +9537,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>80021</t>
+          <t>80019</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -9566,7 +9546,7 @@
         </is>
       </c>
       <c r="D357">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -9587,7 +9567,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>80022</t>
+          <t>80020</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -9596,7 +9576,7 @@
         </is>
       </c>
       <c r="D358">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -9617,7 +9597,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>80023</t>
+          <t>80021</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -9626,7 +9606,7 @@
         </is>
       </c>
       <c r="D359">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -9647,7 +9627,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>80024</t>
+          <t>80022</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -9656,7 +9636,7 @@
         </is>
       </c>
       <c r="D360">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -9665,7 +9645,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -9677,7 +9657,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>80025</t>
+          <t>80023</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -9686,7 +9666,7 @@
         </is>
       </c>
       <c r="D361">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -9695,7 +9675,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -9707,7 +9687,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>80026</t>
+          <t>80024</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -9716,7 +9696,7 @@
         </is>
       </c>
       <c r="D362">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -9737,7 +9717,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>80027</t>
+          <t>80025</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -9746,11 +9726,11 @@
         </is>
       </c>
       <c r="D363">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -9767,7 +9747,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>80028</t>
+          <t>80026</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -9776,7 +9756,7 @@
         </is>
       </c>
       <c r="D364">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -9797,7 +9777,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>80029</t>
+          <t>80027</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -9806,11 +9786,11 @@
         </is>
       </c>
       <c r="D365">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -9827,7 +9807,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>80031</t>
+          <t>80028</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -9836,11 +9816,11 @@
         </is>
       </c>
       <c r="D366">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -9857,7 +9837,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>80032</t>
+          <t>80029</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -9866,7 +9846,7 @@
         </is>
       </c>
       <c r="D367">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -9887,7 +9867,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>80033</t>
+          <t>80031</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -9896,11 +9876,11 @@
         </is>
       </c>
       <c r="D368">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -9917,7 +9897,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>80034</t>
+          <t>80032</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -9926,7 +9906,7 @@
         </is>
       </c>
       <c r="D369">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -9935,7 +9915,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>HC</t>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -9947,7 +9927,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>80035</t>
+          <t>80033</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -9956,16 +9936,16 @@
         </is>
       </c>
       <c r="D370">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>HC</t>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -9977,7 +9957,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>80038</t>
+          <t>80034</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -9986,7 +9966,7 @@
         </is>
       </c>
       <c r="D371">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -10007,7 +9987,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>80039</t>
+          <t>80035</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -10016,7 +9996,7 @@
         </is>
       </c>
       <c r="D372">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -10037,7 +10017,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>80040</t>
+          <t>80038</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -10046,16 +10026,16 @@
         </is>
       </c>
       <c r="D373">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -10067,7 +10047,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>80041</t>
+          <t>80039</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -10076,7 +10056,7 @@
         </is>
       </c>
       <c r="D374">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -10097,7 +10077,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>80043</t>
+          <t>80040</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -10106,7 +10086,7 @@
         </is>
       </c>
       <c r="D375">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -10115,7 +10095,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>HC</t>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -10127,7 +10107,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>80044</t>
+          <t>80041</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -10136,16 +10116,16 @@
         </is>
       </c>
       <c r="D376">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -10157,7 +10137,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>80045</t>
+          <t>80043</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -10166,7 +10146,7 @@
         </is>
       </c>
       <c r="D377">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -10187,7 +10167,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>80046</t>
+          <t>80044</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -10196,16 +10176,16 @@
         </is>
       </c>
       <c r="D378">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>HC</t>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10197,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>80048</t>
+          <t>80045</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -10226,7 +10206,7 @@
         </is>
       </c>
       <c r="D379">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -10235,7 +10215,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -10247,7 +10227,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>80049</t>
+          <t>80046</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -10256,11 +10236,16 @@
         </is>
       </c>
       <c r="D380">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>male</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -10272,12 +10257,25 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>80050</t>
+          <t>80048</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="D381">
+        <v>57</v>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -10289,7 +10287,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>80052</t>
+          <t>80049</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -10298,11 +10296,11 @@
         </is>
       </c>
       <c r="D382">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -10314,20 +10312,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>80054</t>
+          <t>80050</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D383">
-        <v>21</v>
-      </c>
-      <c r="E383" t="inlineStr">
-        <is>
-          <t>female</t>
         </is>
       </c>
     </row>
@@ -10339,7 +10329,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>80055</t>
+          <t>80052</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -10348,7 +10338,7 @@
         </is>
       </c>
       <c r="D384">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -10364,12 +10354,20 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>80056</t>
+          <t>80054</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="D385">
+        <v>21</v>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -10381,7 +10379,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>80058</t>
+          <t>80055</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -10390,7 +10388,7 @@
         </is>
       </c>
       <c r="D386">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -10406,20 +10404,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>80062</t>
+          <t>80056</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D387">
-        <v>47</v>
-      </c>
-      <c r="E387" t="inlineStr">
-        <is>
-          <t>male</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10421,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>80063</t>
+          <t>80058</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -10440,7 +10430,7 @@
         </is>
       </c>
       <c r="D388">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -10456,7 +10446,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>80064</t>
+          <t>80062</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -10465,7 +10455,7 @@
         </is>
       </c>
       <c r="D389">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -10481,25 +10471,20 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>90001</t>
+          <t>80063</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D390">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>female</t>
-        </is>
-      </c>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>patient</t>
         </is>
       </c>
     </row>
@@ -10511,17 +10496,20 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>90002</t>
+          <t>80064</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F391" t="inlineStr">
-        <is>
-          <t>patient</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D391">
+        <v>26</v>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -10533,7 +10521,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>90003</t>
+          <t>90001</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -10542,7 +10530,7 @@
         </is>
       </c>
       <c r="D392">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -10563,20 +10551,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>90004</t>
+          <t>90002</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D393">
-        <v>59</v>
-      </c>
-      <c r="E393" t="inlineStr">
-        <is>
-          <t>female</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -10593,7 +10573,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>90005</t>
+          <t>90003</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -10606,7 +10586,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
@@ -10623,7 +10603,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>90006</t>
+          <t>90004</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -10632,7 +10612,7 @@
         </is>
       </c>
       <c r="D395">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
@@ -10653,7 +10633,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>90007</t>
+          <t>90005</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -10662,7 +10642,7 @@
         </is>
       </c>
       <c r="D396">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
@@ -10683,7 +10663,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>90008</t>
+          <t>90006</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -10692,7 +10672,7 @@
         </is>
       </c>
       <c r="D397">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
@@ -10713,7 +10693,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>90009</t>
+          <t>90007</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -10722,11 +10702,11 @@
         </is>
       </c>
       <c r="D398">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
@@ -10743,7 +10723,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>90010</t>
+          <t>90008</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -10752,7 +10732,7 @@
         </is>
       </c>
       <c r="D399">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -10773,7 +10753,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>90011</t>
+          <t>90009</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -10782,7 +10762,7 @@
         </is>
       </c>
       <c r="D400">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
@@ -10803,7 +10783,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>90012</t>
+          <t>90010</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -10812,7 +10792,7 @@
         </is>
       </c>
       <c r="D401">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
@@ -10833,7 +10813,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>90013</t>
+          <t>90011</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -10842,16 +10822,16 @@
         </is>
       </c>
       <c r="D402">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>HC</t>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -10863,7 +10843,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>90014</t>
+          <t>90013</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -10872,7 +10852,7 @@
         </is>
       </c>
       <c r="D403">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
@@ -10893,7 +10873,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>90016</t>
+          <t>90014</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -10902,7 +10882,7 @@
         </is>
       </c>
       <c r="D404">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
@@ -10923,7 +10903,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>90018</t>
+          <t>90016</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -10932,7 +10912,7 @@
         </is>
       </c>
       <c r="D405">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
@@ -10941,7 +10921,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -10953,7 +10933,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>90019</t>
+          <t>90018</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -10962,16 +10942,16 @@
         </is>
       </c>
       <c r="D406">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>HC</t>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -10983,7 +10963,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>90021</t>
+          <t>90019</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -10992,7 +10972,7 @@
         </is>
       </c>
       <c r="D407">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -11013,7 +10993,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>90022</t>
+          <t>90021</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -11022,11 +11002,16 @@
         </is>
       </c>
       <c r="D408">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
           <t>female</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11023,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>90023</t>
+          <t>90022</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -11047,7 +11032,7 @@
         </is>
       </c>
       <c r="D409">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
@@ -11063,7 +11048,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>90024</t>
+          <t>90023</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -11072,61 +11057,63 @@
         </is>
       </c>
       <c r="D410">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>adolescents</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>90024</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D411">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>adolescents</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>90012</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D412">
-        <v>14</v>
+          <t>9</t>
+        </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>female</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -11138,7 +11125,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -11147,7 +11134,7 @@
         </is>
       </c>
       <c r="D413">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
@@ -11163,7 +11150,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -11172,7 +11159,7 @@
         </is>
       </c>
       <c r="D414">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
@@ -11188,7 +11175,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -11197,11 +11184,11 @@
         </is>
       </c>
       <c r="D415">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -11213,7 +11200,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -11222,7 +11209,7 @@
         </is>
       </c>
       <c r="D416">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
@@ -11238,7 +11225,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -11247,7 +11234,7 @@
         </is>
       </c>
       <c r="D417">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
@@ -11263,7 +11250,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -11272,11 +11259,11 @@
         </is>
       </c>
       <c r="D418">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -11288,7 +11275,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>109</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -11297,7 +11284,7 @@
         </is>
       </c>
       <c r="D419">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
@@ -11313,7 +11300,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -11322,7 +11309,7 @@
         </is>
       </c>
       <c r="D420">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
@@ -11338,7 +11325,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -11347,7 +11334,7 @@
         </is>
       </c>
       <c r="D421">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
@@ -11363,7 +11350,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -11372,11 +11359,11 @@
         </is>
       </c>
       <c r="D422">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -11388,7 +11375,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -11397,11 +11384,11 @@
         </is>
       </c>
       <c r="D423">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -11413,7 +11400,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>67</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -11422,7 +11409,7 @@
         </is>
       </c>
       <c r="D424">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E424" t="inlineStr">
         <is>
@@ -11438,7 +11425,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -11447,7 +11434,7 @@
         </is>
       </c>
       <c r="D425">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
@@ -11463,7 +11450,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -11472,7 +11459,7 @@
         </is>
       </c>
       <c r="D426">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
@@ -11488,7 +11475,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -11501,7 +11488,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -11513,7 +11500,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -11522,11 +11509,11 @@
         </is>
       </c>
       <c r="D428">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -11538,7 +11525,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -11547,11 +11534,11 @@
         </is>
       </c>
       <c r="D429">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -11563,7 +11550,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -11572,11 +11559,11 @@
         </is>
       </c>
       <c r="D430">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -11588,7 +11575,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -11597,7 +11584,7 @@
         </is>
       </c>
       <c r="D431">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
@@ -11613,7 +11600,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -11622,11 +11609,11 @@
         </is>
       </c>
       <c r="D432">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -11638,7 +11625,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -11647,7 +11634,7 @@
         </is>
       </c>
       <c r="D433">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
@@ -11663,7 +11650,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -11672,7 +11659,7 @@
         </is>
       </c>
       <c r="D434">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E434" t="inlineStr">
         <is>
@@ -11688,7 +11675,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -11701,7 +11688,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -11713,7 +11700,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>73</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -11722,7 +11709,7 @@
         </is>
       </c>
       <c r="D436">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
@@ -11738,7 +11725,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -11763,7 +11750,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -11772,11 +11759,11 @@
         </is>
       </c>
       <c r="D438">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -11788,7 +11775,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -11813,7 +11800,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>84</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -11822,7 +11809,7 @@
         </is>
       </c>
       <c r="D440">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
@@ -11838,7 +11825,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>94</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -11863,7 +11850,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>124</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -11872,7 +11859,7 @@
         </is>
       </c>
       <c r="D442">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
@@ -11888,7 +11875,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -11897,7 +11884,7 @@
         </is>
       </c>
       <c r="D443">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
@@ -11913,7 +11900,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -11922,11 +11909,11 @@
         </is>
       </c>
       <c r="D444">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -11938,7 +11925,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>135</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -11947,7 +11934,7 @@
         </is>
       </c>
       <c r="D445">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
@@ -11963,7 +11950,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -11972,7 +11959,7 @@
         </is>
       </c>
       <c r="D446">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
@@ -11988,7 +11975,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>105</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -12001,7 +11988,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12013,7 +12000,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>107</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -12022,11 +12009,11 @@
         </is>
       </c>
       <c r="D448">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12025,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -12047,11 +12034,11 @@
         </is>
       </c>
       <c r="D449">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -12063,7 +12050,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -12088,7 +12075,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -12097,11 +12084,11 @@
         </is>
       </c>
       <c r="D451">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12113,7 +12100,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>121</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -12122,7 +12109,7 @@
         </is>
       </c>
       <c r="D452">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E452" t="inlineStr">
         <is>
@@ -12138,7 +12125,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>130</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -12147,7 +12134,7 @@
         </is>
       </c>
       <c r="D453">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E453" t="inlineStr">
         <is>
@@ -12163,7 +12150,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>129</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -12172,11 +12159,11 @@
         </is>
       </c>
       <c r="D454">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -12188,7 +12175,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>117</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -12197,11 +12184,11 @@
         </is>
       </c>
       <c r="D455">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -12213,7 +12200,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>126</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -12226,7 +12213,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12238,7 +12225,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>103</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -12247,7 +12234,7 @@
         </is>
       </c>
       <c r="D457">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E457" t="inlineStr">
         <is>
@@ -12263,7 +12250,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>113</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -12272,7 +12259,7 @@
         </is>
       </c>
       <c r="D458">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E458" t="inlineStr">
         <is>
@@ -12288,7 +12275,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>110</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -12297,7 +12284,7 @@
         </is>
       </c>
       <c r="D459">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
@@ -12313,7 +12300,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>119</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -12338,7 +12325,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>141</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -12347,7 +12334,7 @@
         </is>
       </c>
       <c r="D461">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
@@ -12363,7 +12350,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>147</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -12372,11 +12359,11 @@
         </is>
       </c>
       <c r="D462">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -12388,7 +12375,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>161</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -12397,11 +12384,11 @@
         </is>
       </c>
       <c r="D463">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12413,7 +12400,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>139</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -12422,7 +12409,7 @@
         </is>
       </c>
       <c r="D464">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
@@ -12438,7 +12425,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>144</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -12447,7 +12434,7 @@
         </is>
       </c>
       <c r="D465">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
@@ -12463,7 +12450,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>166</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -12472,7 +12459,7 @@
         </is>
       </c>
       <c r="D466">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E466" t="inlineStr">
         <is>
@@ -12488,7 +12475,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>150</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -12497,7 +12484,7 @@
         </is>
       </c>
       <c r="D467">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E467" t="inlineStr">
         <is>
@@ -12513,7 +12500,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>151</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -12522,7 +12509,7 @@
         </is>
       </c>
       <c r="D468">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E468" t="inlineStr">
         <is>
@@ -12538,7 +12525,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>165</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -12563,7 +12550,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>156</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -12572,11 +12559,11 @@
         </is>
       </c>
       <c r="D470">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12588,7 +12575,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>158</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -12597,11 +12584,11 @@
         </is>
       </c>
       <c r="D471">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -12613,7 +12600,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>154</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -12622,11 +12609,11 @@
         </is>
       </c>
       <c r="D472">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -12638,7 +12625,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>163</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -12647,11 +12634,11 @@
         </is>
       </c>
       <c r="D473">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12663,7 +12650,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>176</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -12672,7 +12659,7 @@
         </is>
       </c>
       <c r="D474">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
@@ -12688,7 +12675,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>224</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -12697,11 +12684,11 @@
         </is>
       </c>
       <c r="D475">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -12713,7 +12700,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>175</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -12722,7 +12709,7 @@
         </is>
       </c>
       <c r="D476">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
@@ -12738,7 +12725,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>168</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -12747,11 +12734,11 @@
         </is>
       </c>
       <c r="D477">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12763,7 +12750,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>173</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -12772,7 +12759,7 @@
         </is>
       </c>
       <c r="D478">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
@@ -12788,7 +12775,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>169</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -12797,7 +12784,7 @@
         </is>
       </c>
       <c r="D479">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
@@ -12813,7 +12800,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>180</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -12822,11 +12809,11 @@
         </is>
       </c>
       <c r="D480">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12838,7 +12825,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -12847,11 +12834,11 @@
         </is>
       </c>
       <c r="D481">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -12863,7 +12850,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>209</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -12872,7 +12859,7 @@
         </is>
       </c>
       <c r="D482">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E482" t="inlineStr">
         <is>
@@ -12888,7 +12875,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>191</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -12897,11 +12884,11 @@
         </is>
       </c>
       <c r="D483">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12913,7 +12900,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -12922,11 +12909,11 @@
         </is>
       </c>
       <c r="D484">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -12938,7 +12925,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>196</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -12947,7 +12934,7 @@
         </is>
       </c>
       <c r="D485">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E485" t="inlineStr">
         <is>
@@ -12963,7 +12950,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -12972,11 +12959,11 @@
         </is>
       </c>
       <c r="D486">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12988,7 +12975,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>186</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -12997,7 +12984,12 @@
         </is>
       </c>
       <c r="D487">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
       </c>
     </row>
     <row r="488">
@@ -13008,7 +13000,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>193</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -13017,11 +13009,11 @@
         </is>
       </c>
       <c r="D488">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13033,7 +13025,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>203</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -13042,12 +13034,7 @@
         </is>
       </c>
       <c r="D489">
-        <v>15</v>
-      </c>
-      <c r="E489" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
+        <v>17</v>
       </c>
     </row>
     <row r="490">
@@ -13058,7 +13045,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>205</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -13067,7 +13054,7 @@
         </is>
       </c>
       <c r="D490">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
@@ -13083,7 +13070,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>210</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -13092,11 +13079,11 @@
         </is>
       </c>
       <c r="D491">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13108,7 +13095,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>207</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -13117,11 +13104,11 @@
         </is>
       </c>
       <c r="D492">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13120,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>212</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -13142,7 +13129,7 @@
         </is>
       </c>
       <c r="D493">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E493" t="inlineStr">
         <is>
@@ -13158,7 +13145,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>215</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -13167,11 +13154,11 @@
         </is>
       </c>
       <c r="D494">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13183,7 +13170,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>218</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -13192,11 +13179,11 @@
         </is>
       </c>
       <c r="D495">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13208,7 +13195,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>229</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -13221,7 +13208,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13233,12 +13220,20 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
           <t>7</t>
+        </is>
+      </c>
+      <c r="D497">
+        <v>16</v>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13250,7 +13245,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>223</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -13259,11 +13254,11 @@
         </is>
       </c>
       <c r="D498">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13275,20 +13270,12 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>227</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D499">
-        <v>13</v>
-      </c>
-      <c r="E499" t="inlineStr">
-        <is>
-          <t>male</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13287,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>221</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -13309,11 +13296,11 @@
         </is>
       </c>
       <c r="D500">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13325,7 +13312,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>269</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -13334,11 +13321,11 @@
         </is>
       </c>
       <c r="D501">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13350,7 +13337,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>232</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -13359,7 +13346,7 @@
         </is>
       </c>
       <c r="D502">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E502" t="inlineStr">
         <is>
@@ -13375,7 +13362,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>228</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -13384,11 +13371,11 @@
         </is>
       </c>
       <c r="D503">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13400,7 +13387,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>241</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -13425,7 +13412,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>261</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -13434,7 +13421,7 @@
         </is>
       </c>
       <c r="D505">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E505" t="inlineStr">
         <is>
@@ -13450,7 +13437,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>248</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -13459,11 +13446,11 @@
         </is>
       </c>
       <c r="D506">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13475,7 +13462,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>251</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -13484,7 +13471,7 @@
         </is>
       </c>
       <c r="D507">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E507" t="inlineStr">
         <is>
@@ -13500,7 +13487,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>245</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -13509,11 +13496,11 @@
         </is>
       </c>
       <c r="D508">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13525,12 +13512,20 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>253</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
           <t>7</t>
+        </is>
+      </c>
+      <c r="D509">
+        <v>17</v>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13542,7 +13537,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>265</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -13551,7 +13546,7 @@
         </is>
       </c>
       <c r="D510">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E510" t="inlineStr">
         <is>
@@ -13567,20 +13562,12 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>278</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D511">
-        <v>16</v>
-      </c>
-      <c r="E511" t="inlineStr">
-        <is>
-          <t>female</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13579,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>247</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -13605,7 +13592,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13604,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>250</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -13642,7 +13629,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>270</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -13655,7 +13642,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13667,7 +13654,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>263</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -13678,6 +13665,11 @@
       <c r="D515">
         <v>16</v>
       </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -13687,7 +13679,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>239</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -13696,11 +13688,11 @@
         </is>
       </c>
       <c r="D516">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13712,7 +13704,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>259</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -13721,12 +13713,7 @@
         </is>
       </c>
       <c r="D517">
-        <v>15</v>
-      </c>
-      <c r="E517" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
+        <v>16</v>
       </c>
     </row>
     <row r="518">
@@ -13737,7 +13724,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>242</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -13746,7 +13733,7 @@
         </is>
       </c>
       <c r="D518">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E518" t="inlineStr">
         <is>
@@ -13762,12 +13749,20 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>279</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
           <t>7</t>
+        </is>
+      </c>
+      <c r="D519">
+        <v>15</v>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13774,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>258</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -13788,11 +13783,11 @@
         </is>
       </c>
       <c r="D520">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13804,18 +13799,102 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>adolescents</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>adolescents</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D523">
+        <v>17</v>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>adolescents</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D524">
+        <v>16</v>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>adolescents</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
           <t>474</t>
         </is>
       </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D521">
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D525">
         <v>16</v>
       </c>
-      <c r="E521" t="inlineStr">
+      <c r="E525" t="inlineStr">
         <is>
           <t>female</t>
         </is>
